--- a/data/trans_orig/Q20A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que ha estado hospitalizado en los últimos 12 meses</t>
+          <t>Número medio de veces que la población ha estado hospitalizada en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,09</t>
+          <t>0,03; 0,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,08; 0,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,14</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,59</t>
+          <t>0,05; 0,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,11</t>
+          <t>0,04; 0,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,41</t>
+          <t>0,06; 0,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,08</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,21</t>
+          <t>0,06; 0,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,22</t>
+          <t>0,03; 0,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,22</t>
+          <t>0,07; 0,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,21</t>
+          <t>0,07; 0,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,18</t>
+          <t>0,07; 0,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,2</t>
+          <t>0,04; 0,21</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,11</t>
+          <t>0,05; 0,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,08</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,18</t>
+          <t>0,1; 0,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,13</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,14</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,17</t>
+          <t>0,06; 0,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,21</t>
+          <t>0,12; 0,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,06; 0,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1416,27 +1416,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,04</t>
+          <t>0,0; 0,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,05</t>
+          <t>0,01; 0,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,09</t>
+          <t>0,02; 0,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,04</t>
+          <t>0,0; 0,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,14</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">

--- a/data/trans_orig/Q20A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Clase-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,1</t>
+          <t>0,03; 0,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,1</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,12</t>
+          <t>0,04; 0,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,32 +746,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,16</t>
+          <t>0,07; 0,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>0,07; 0,15</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,13</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,13</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,12</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>0,06; 0,11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,13</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,14</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,12</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,1</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,57</t>
+          <t>0,04; 0,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,12</t>
+          <t>0,04; 0,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,35</t>
+          <t>0,07; 0,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,13</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,37 +1006,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,07; 0,21</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,36</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,15</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,17</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>0,06; 0,24</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 0,26</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,16</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,16</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,23</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,07; 0,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,2</t>
+          <t>0,07; 0,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,21</t>
+          <t>0,08; 0,32</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,1</t>
+          <t>0,05; 0,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,18</t>
+          <t>0,09; 0,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,1</t>
+          <t>0,07; 0,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,08; 0,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,07; 0,17</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,13</t>
+          <t>0,04; 0,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,07; 0,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,22</t>
+          <t>0,11; 0,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,1</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,05</t>
+          <t>0,0; 0,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,06</t>
+          <t>0,01; 0,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,05</t>
+          <t>0,01; 0,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,07</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
     </row>
@@ -1503,27 +1503,27 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1561,22 +1561,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0,07; 0,13</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,08</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>0,07; 0,14</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,08</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,12</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,09; 0,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,07; 0,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
     </row>
